--- a/Excel-Finance/Finance-And-Accounting-01/Index and Match.xlsx
+++ b/Excel-Finance/Finance-And-Accounting-01/Index and Match.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\books-and-tutorials\Finance-Excel\Part 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel-Finance\Finance-And-Accounting-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E23080-4C59-4345-9C13-87FDC59BF401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB218E3-92B2-4C02-A267-FC1A0307BD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -737,9 +737,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -777,7 +777,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -883,7 +883,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1025,7 +1025,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1034,16 +1034,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I58"/>
-  <sheetFormatPr defaultColWidth="15.28515625" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="3"/>
-    <col min="2" max="2" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="15.28515625" style="3"/>
-    <col min="7" max="7" width="15.28515625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="15.28515625" style="3"/>
+    <col min="1" max="1" width="15.33203125" style="3"/>
+    <col min="2" max="2" width="17.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="15.33203125" style="3"/>
+    <col min="7" max="7" width="15.33203125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="15.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1054,7 @@
       <c r="G1" s="3"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <f>INDEX(A4:G58,4,6)</f>
         <v>0.63019166666666659</v>
@@ -1067,10 +1067,10 @@
       <c r="G2" s="4"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C3" s="6"/>
     </row>
-    <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>43</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>18.77</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>50</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>688.31</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>24</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>756.2299999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>42</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>844.78</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>47</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>1079.73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>13</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>1200.01</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>46</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>1205.8899999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>1211.3100000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>54</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>2264.71</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>35</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>2359.62</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>51</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>2840.36</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>21</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>3029.1800000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>19</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>3683.31</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>34</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>3694.71</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>53</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>4088.73</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>49</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>4163.8900000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>29</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>4221.84</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>45</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>4296.04</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>8</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>4368.79</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>9</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>4496.8500000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>36</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>4550.4800000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>12</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>5950.74</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>27</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>6073.68</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>30</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>6334.09</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>1</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>6601</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>22</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>6872.78</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>5</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>7367.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>6</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>7455.5300000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>18</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>7455.5300000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>2</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>8245</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>37</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>8300.57</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>7</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>8319.85</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>17</v>
       </c>
@@ -1878,14 +1878,14 @@
         <v>21</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" ref="F37:F68" si="1">G37/1200</f>
+        <f t="shared" ref="F37:F58" si="1">G37/1200</f>
         <v>6.9458583333333328</v>
       </c>
       <c r="G37" s="5">
         <v>8335.0299999999988</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>31</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>8335.0299999999988</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>41</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>8625.5500000000011</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>8984.2200000000012</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>14</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>9051.61</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>9892.91</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>33</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>10046.65</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>25</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>10122.48</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>23</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>10516.82</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>15</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>10820.95</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>10878.73</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>39</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>10927.05</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>26</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>11899.01</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>11</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>12044.96</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>28</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>12044.96</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>52</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>12068.25</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>16</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>12626.68</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>20</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>13447.53</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>48</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>13510.36</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>3</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>13683</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>4</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>14108.48</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>32</v>
       </c>
@@ -2401,14 +2401,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C159A4-28E0-472E-B512-61BA5EC25F7A}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>130</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>132</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>133</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>134</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>135</v>
       </c>
@@ -2467,9 +2467,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1F1E5A-1573-4154-ADD3-2C997B30B98F}">
   <dimension ref="B1:I10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>118</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>69</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>122</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>123</v>
       </c>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>124</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>4556</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>125</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>3656</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>126</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>5321</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>127</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>128</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -2636,14 +2636,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD3D7B2-CA82-4F3B-A742-B20B0F394F0F}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>137</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="M1" s="13"/>
       <c r="N1" s="13"/>
     </row>
-    <row r="2" spans="1:14" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="M2" s="14"/>
       <c r="N2" s="14"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
